--- a/mistral_translate_work/split_by_prompt/excel/weapon/lang_weapon/lang_weapon__weapon__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/weapon/lang_weapon/lang_weapon__weapon__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Lưỡi kiếm sinh ra để phụng sự công lý. Những hoa văn giống như biểu tượng của pháp luật được khắc trên thân kiếm. Thề trên liên minh, vinh quang sẽ đến!</t>
+          <t>Lưỡi kiếm sinh ra để phụng sự pháp luật. Những hoa văn giống như biểu tượng của pháp luật được khắc trên thân kiếm. Thề trên liên minh, vinh quang sẽ đến!</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Lưỡi kiếm sinh ra để phụng sự công lý. Những hoa văn giống như biểu tượng của pháp luật được khắc trên thân kiếm. Thề trên liên minh, vinh quang sẽ đến!</t>
+          <t>Lưỡi kiếm sinh ra để phụng sự pháp luật. Những hoa văn giống như biểu tượng của pháp luật được khắc trên thân kiếm. Thề trên liên minh, vinh quang sẽ đến!</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Lưỡi đao rộng chứa đựng ý chí tập thể. Bất cứ nơi nào nó đi qua, sức mạnh đoàn kết bất khả chiến bại đều được hiện thực hóa.</t>
+          <t>Một thanh Đại kiếm chứa đựng ý chí tập thể. Bất cứ nơi nào nó đi qua, sức mạnh đoàn kết không thể phá vỡ đều hiện lộ.</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>"Qua đêm dài, vinh quang sẽ đến." Khắc trên Thanh Trường Kiếm không chỉ là lời thề bảo vệ, mà còn là quyết tâm của người chiến binh.</t>
+          <t>"Qua đêm dài, vinh quang sẽ đến." Khắc trên Đại kiếm không chỉ là lời thề bảo vệ, mà còn là quyết tâm của người chiến binh.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>"Qua đêm dài, vinh quang sẽ đến." Khắc trên Thanh Trường Kiếm không chỉ là lời thề bảo vệ, mà còn là quyết tâm của người chiến binh.</t>
+          <t>"Qua đêm dài, vinh quang sẽ đến." Khắc trên Đại kiếm không chỉ là lời thề bảo vệ, mà còn là quyết tâm của người chiến binh.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Một thanh trường kiếm nặng hơn nghìn cân. Chỉ riêng sự hỗn loạn từ việc vung kiếm cũng đủ để xé nát kẻ thù.</t>
+          <t>Một thanh kiếm bản rộng nặng hơn nghìn cân. Chỉ riêng luồng chấn động khi vung kiếm cũng đủ xé nát kẻ thù.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>"Qua đêm dài, vinh quang sẽ đến." Khắc trên Thanh Đoản Kiếm không chỉ là lời thề bảo vệ, mà còn là khát vọng của người chiến binh.</t>
+          <t>"Qua đêm dài, vinh quang sẽ đến." Khắc trên Kiếm không chỉ là lời thề bảo vệ, mà còn là khát vọng của người chiến binh.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>"Qua đêm dài, vinh quang sẽ đến." Khắc trên Thanh Đoản Kiếm không chỉ là lời thề bảo vệ, mà còn là khát vọng của người chiến binh.</t>
+          <t>"Qua đêm dài, vinh quang sẽ đến." Khắc trên Kiếm không chỉ là lời thề bảo vệ, mà còn là khát vọng của người chiến binh.</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Khi HP cao hơn {0}%, tỷ lệ chí mạng của nhân vật tăng {1}%.</t>
+          <t>Khi HP cao hơn {0}%, Crit. Rate của nhân vật tăng {1}%.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>"Qua đêm dài, đến ngày thắng lợi." Khắc trên Rectifier không chỉ là lời thề của người bảo vệ, mà còn là sự tự tin rực cháy.</t>
+          <t>"Qua đêm dài, đến ngày thắng lợi." Khắc trên Pháp khí không chỉ là lời thề của người bảo vệ, mà còn là sự tự tin rực cháy.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>"Qua đêm dài, đến ngày thắng lợi." Khắc trên Rectifier không chỉ là lời thề của người bảo vệ, mà còn là sự tự tin rực cháy.</t>
+          <t>"Qua đêm dài, đến ngày thắng lợi." Khắc trên Pháp khí không chỉ là lời thề của người bảo vệ, mà còn là sự tự tin rực cháy.</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Khởi Đầu Của Cuộc Tranh Tài. Một lưỡi Broadblade được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
+          <t>Khởi Đầu Của Cuộc Tranh Tài. Một thanh Đại kiếm được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Khởi Đầu Của Cuộc Tranh Tài. Một lưỡi Broadblade được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
+          <t>Khởi Đầu Của Cuộc Tranh Tài. Một thanh Đại kiếm được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Một lưỡi Broadblade được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
+          <t>Một thanh Đại kiếm được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Khởi Đầu Của Những Waves Cách Mạng. Một lưỡi Smallblade được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
+          <t>Khởi đầu của làn sóng cách mạng. Một thanh Kiếm được chế tạo đặc biệt cho Resonator mới. Dưới vẻ ngoài giản dị ấy ẩn chứa sức mạnh không thể xem thường.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Khởi Đầu Của Những Waves Cách Mạng. Một lưỡi Smallblade được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
+          <t>Khởi đầu của làn sóng cách mạng. Một thanh Kiếm được chế tạo đặc biệt cho Resonator mới. Dưới vẻ ngoài giản dị ấy ẩn chứa sức mạnh không thể xem thường.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Một lưỡi Smallblade được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
+          <t>Một thanh Kiếm được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Khởi Nguyên của Vạn Vật. Một Rectifier được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
+          <t>Khởi Nguyên của Vạn Vật. Một Pháp khí được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Khởi Nguyên của Vạn Vật. Một Rectifier được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
+          <t>Khởi Nguyên của Vạn Vật. Một Pháp khí được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Một Rectifier được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
+          <t>Một Pháp khí được chế tạo đặc biệt cho Resonators mới. Ẩn chứa sức mạnh không thể xem thường dưới vẻ ngoài đơn giản.</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Một Broadblade được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
+          <t>Một thanh Đại kiếm được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Một Broadblade được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
+          <t>Một thanh Đại kiếm được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Một Broadblade được chế tạo cho huấn luyện chiến đấu, chỉ dùng cho các động tác chiến đấu cơ bản.</t>
+          <t>Một thanh Đại kiếm được chế tạo cho huấn luyện chiến đấu, chỉ dùng cho các động tác chiến đấu cơ bản.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Một Smallblade được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
+          <t>Một thanh Kiếm được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Một Smallblade được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
+          <t>Một thanh Kiếm được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Một Smallblade được chế tạo cho huấn luyện chiến đấu. Chỉ dùng cho các trận chiến cơ bản.</t>
+          <t>Một thanh Kiếm được chế tạo cho huấn luyện chiến đấu. Chỉ dùng cho các trận chiến cơ bản.</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Một Pistol được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
+          <t>Một khẩu Súng được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Một Pistol được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
+          <t>Một khẩu Súng được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Một Gun được chế tạo cho huấn luyện chiến đấu. Chỉ dùng cho các trận chiến cơ bản.</t>
+          <t>Một khẩu Súng được chế tạo cho huấn luyện chiến đấu. Chỉ dùng cho các trận chiến cơ bản.</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Một Gauntlet được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
+          <t>Một bộ Găng tay được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Một Gauntlet được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
+          <t>Một bộ Găng tay được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Một Gauntlet được chế tạo cho huấn luyện chiến đấu. Chỉ dùng cho các trận chiến cơ bản.</t>
+          <t>Một bộ Găng tay được chế tạo cho huấn luyện chiến đấu. Chỉ dùng cho các trận chiến cơ bản.</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Một Rectifier được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
+          <t>Một Pháp khí được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Một Rectifier được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
+          <t>Một Pháp khí được chế tạo cho việc huấn luyện và giảng dạy. Chỉ bao gồm các khả năng thiết yếu.</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Một Rectifier được chế tạo cho huấn luyện chiến đấu. Chỉ dùng cho các trận chiến cơ bản.</t>
+          <t>Một Pháp khí được chế tạo cho huấn luyện chiến đấu. Chỉ dùng cho các trận chiến cơ bản.</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Mã hiệu REGULARIZATION, nguyên mẫu Broadblade, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
+          <t>Mã hiệu REGULARIZATION, nguyên mẫu Đại kiếm, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Mã hiệu REGULARIZATION, nguyên mẫu Broadblade, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
+          <t>Mã hiệu REGULARIZATION, nguyên mẫu Đại kiếm, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Mã hiệu REGULARIZATION, nguyên mẫu Broadblade, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
+          <t>Mã hiệu REGULARIZATION, nguyên mẫu Đại kiếm, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Mã hiệu SPEAR, nguyên mẫu Smallblade, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
+          <t>Mã hiệu SPEAR, nguyên mẫu Kiếm, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Mã hiệu SPEAR, nguyên mẫu Smallblade, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
+          <t>Mã hiệu SPEAR, nguyên mẫu Kiếm, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Mã hiệu SPEAR, nguyên mẫu Smallblade, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
+          <t>Mã hiệu SPEAR, nguyên mẫu Kiếm, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Mã hiệu SEQUENCE, nguyên mẫu Rectifier, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
+          <t>Mã hiệu SEQUENCE, nguyên mẫu Pháp khí, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Mã hiệu SEQUENCE, nguyên mẫu Rectifier, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
+          <t>Mã hiệu SEQUENCE, nguyên mẫu Pháp khí, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Mã hiệu SEQUENCE, nguyên mẫu Rectifier, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
+          <t>Mã hiệu SEQUENCE, nguyên mẫu Pháp khí, từ dự án vũ khí sản xuất hàng loạt thế hệ tiếp theo của Huanglong.</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Phiên bản cải tiến của nguyên mẫu Broadblade từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với hiệu suất mạnh mẽ và công nghệ tiên tiến, thanh long này mang sức nặng chỉ có những chiến binh trải qua nhiều năm rèn luyện mới có thể sử dụng.</t>
+          <t>Phiên bản cải tiến của nguyên mẫu Đại kiếm từ dự án vũ khí sản xuất hàng loạt thế hệ mới của Huanglong. Với hiệu năng mạnh mẽ và công nghệ mới lạ, con rồng này mang sức nặng mà chỉ những chiến binh trải qua nhiều năm rèn luyện mới có thể sử dụng.</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Phiên bản cải tiến của nguyên mẫu Broadblade từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với hiệu suất mạnh mẽ và công nghệ tiên tiến, thanh long này mang sức nặng chỉ có những chiến binh trải qua nhiều năm rèn luyện mới có thể sử dụng.</t>
+          <t>Phiên bản cải tiến của nguyên mẫu Đại kiếm từ dự án vũ khí sản xuất hàng loạt thế hệ mới của Huanglong. Với hiệu năng mạnh mẽ và công nghệ mới lạ, con rồng này mang sức nặng mà chỉ những chiến binh trải qua nhiều năm rèn luyện mới có thể sử dụng.</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Phiên bản cải tiến của nguyên mẫu Broadblade từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với hiệu suất mạnh mẽ và công nghệ tiên tiến, thanh long này mang sức nặng chỉ có những chiến binh trải qua nhiều năm rèn luyện mới có thể sử dụng.</t>
+          <t>Phiên bản cải tiến của nguyên mẫu Đại kiếm từ dự án vũ khí sản xuất hàng loạt thế hệ mới của Huanglong. Với hiệu năng mạnh mẽ và công nghệ mới lạ, con rồng này mang sức nặng mà chỉ những chiến binh trải qua nhiều năm rèn luyện mới có thể sử dụng.</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Phiên bản cải tiến của nguyên mẫu Smallblade từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với lưỡi kiếm được tinh giản và thiết kế tối ưu, nó chỉ vừa vặn trong lòng bàn tay của những kiếm khách lão luyện.</t>
+          <t>Phiên bản cải tiến của nguyên mẫu Kiếm từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với lưỡi kiếm được tinh giản và thiết kế tối ưu, nó chỉ vừa vặn trong lòng bàn tay của những kiếm khách lão luyện.</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Phiên bản cải tiến của nguyên mẫu Smallblade từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với lưỡi kiếm được tinh giản và thiết kế tối ưu, nó chỉ vừa vặn trong lòng bàn tay của những kiếm khách lão luyện.</t>
+          <t>Phiên bản cải tiến của nguyên mẫu Kiếm từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với lưỡi kiếm được tinh giản và thiết kế tối ưu, nó chỉ vừa vặn trong lòng bàn tay của những kiếm khách lão luyện.</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Phiên bản cải tiến của nguyên mẫu Smallblade từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với lưỡi kiếm được tinh giản và thiết kế tối ưu, nó chỉ vừa vặn trong lòng bàn tay của những kiếm khách lão luyện.</t>
+          <t>Phiên bản cải tiến của nguyên mẫu Kiếm từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với lưỡi kiếm được tinh giản và thiết kế tối ưu, nó chỉ vừa vặn trong lòng bàn tay của những kiếm khách lão luyện.</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Phiên bản cải tiến của nguyên mẫu Broadblade từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với sức mạnh trào dâng và thấu kính được tinh luyện cao độ, thanh âm của nó chỉ có thể được vang lên bởi những người có ý chí sắt thép.</t>
+          <t>Phiên bản cải tiến của nguyên mẫu Đại kiếm từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với sức mạnh trào dâng và thấu kính được tinh luyện cao độ, thanh âm của nó chỉ có thể được vang lên bởi những người có ý chí sắt thép.</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Phiên bản cải tiến của nguyên mẫu Broadblade từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với sức mạnh trào dâng và thấu kính được tinh luyện cao độ, thanh âm của nó chỉ có thể được vang lên bởi những người có ý chí sắt thép.</t>
+          <t>Phiên bản cải tiến của nguyên mẫu Đại kiếm từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với sức mạnh trào dâng và thấu kính được tinh luyện cao độ, thanh âm của nó chỉ có thể được vang lên bởi những người có ý chí sắt thép.</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Phiên bản cải tiến của nguyên mẫu Broadblade từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với sức mạnh trào dâng và thấu kính được tinh luyện cao độ, thanh âm của nó chỉ có thể được vang lên bởi những người có ý chí sắt thép.</t>
+          <t>Phiên bản cải tiến của nguyên mẫu Đại kiếm từ dự án vũ khí sản xuất hàng loạt thế hệ mới Huanglong. Với sức mạnh trào dâng và thấu kính được tinh luyện cao độ, thanh âm của nó chỉ có thể được vang lên bởi những người có ý chí sắt thép.</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Vũ khí đặc biệt được chế tạo cho Midnight Rangers để tưởng nhớ lòng dũng cảm của họ. Một bài thơ ca ngợi họ: "Ngàn tiếng vang truyền tin chiến trận, tất cả đều đoàn kết trong Hẻm Núi tinh thần."</t>
+          <t>Vũ khí đặc biệt được chế tạo cho Midnight Rangers để tưởng nhớ lòng dũng cảm của họ. Một bài thơ ca ngợi họ: "Ngàn tiếng vang truyền tin chiến trận, mọi người cùng đoàn kết tại Gorges of spirit.</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Vũ khí đặc biệt được chế tạo cho Midnight Rangers để tưởng nhớ lòng dũng cảm của họ. Một bài thơ ca ngợi họ: "Ngàn tiếng vang truyền tin chiến trận, tất cả đều đoàn kết trong Hẻm Núi tinh thần."</t>
+          <t>Vũ khí đặc biệt được chế tạo cho Midnight Rangers để tưởng nhớ lòng dũng cảm của họ. Một bài thơ ca ngợi họ: "Ngàn tiếng vang truyền tin chiến trận, mọi người cùng đoàn kết tại Gorges of spirit.</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Vũ khí đặc biệt được chế tạo cho Midnight Rangers để tưởng nhớ lòng dũng cảm của họ. Một bài thơ ca ngợi họ: "Ngàn tiếng vang truyền tin chiến trận, tất cả đều đoàn kết trong Hẻm Núi tinh thần."</t>
+          <t>Vũ khí đặc biệt được chế tạo cho Midnight Rangers để tưởng nhớ lòng dũng cảm của họ. Một bài thơ ca ngợi họ: "Ngàn tiếng vang truyền tin chiến trận, mọi người cùng đoàn kết tại Gorges of spirit.</t>
         </is>
       </c>
     </row>
